--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/parttimer_jure.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/parttimer_jure.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="fiama" sheetId="1" r:id="rId3"/>
+    <sheet name="fiama" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -126,29 +126,6 @@
   </si>
   <si>
     <t xml:space="preserve">Shit!</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">朱亚教团目前正在进行由其他神改信朱亚的活动。
-现在改信可以免受惩罚！信仰天数也可以延续！而且还赠送免费、数量有限的朱亚抱枕！
-客人…可不要错过这个难得的机会啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不要</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的，真的要改信吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">谢咯！终于完成今天的定额了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啧！</t>
   </si>
 </sst>
 </file>
@@ -169,19 +146,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -200,7 +177,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -209,46 +186,46 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -262,13 +239,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -444,25 +421,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.14" style="1" customWidth="1"/>
-    <col min="10" max="10" width="53.28" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,29 +474,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="95.5">
-      <c r="H11" s="1">
+    <row r="11" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -528,18 +505,15 @@
       <c r="J11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" ht="12.8">
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -548,18 +522,15 @@
       <c r="J12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" ht="12.8">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -568,22 +539,19 @@
       <c r="J13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" ht="12.8">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" ht="22.35">
-      <c r="H21" s="1">
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
@@ -592,18 +560,15 @@
       <c r="J21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" ht="12.8">
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -612,18 +577,15 @@
       <c r="J22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" ht="12.8">
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -632,17 +594,14 @@
       <c r="J23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" ht="12.8">
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
-      <c r="H27" s="1">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -651,11 +610,8 @@
       <c r="J27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" ht="12.8">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
         <v>29</v>
       </c>
@@ -663,18 +619,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
-      <c r="H32" s="1">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -683,23 +639,20 @@
       <c r="J32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" ht="12.8">
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/parttimer_jure.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/parttimer_jure.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="fiama" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="fiama" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -126,6 +126,29 @@
   </si>
   <si>
     <t xml:space="preserve">Shit!</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">朱亚教团目前正在进行由其他神改信朱亚的活动。
+现在改信可以免受惩罚！信仰天数也可以延续！而且还赠送免费、数量有限的朱亚抱枕！
+客人…可不要错过这个难得的机会啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不要</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的，真的要改信吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">谢咯！终于完成今天的定额了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啧！</t>
   </si>
 </sst>
 </file>
@@ -146,19 +169,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -177,7 +200,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -186,46 +209,46 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -239,13 +262,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -421,25 +444,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.28"/>
+    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="53.28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,29 +497,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H11" s="1" t="n">
+    <row r="11" ht="95.5">
+      <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -505,15 +528,18 @@
       <c r="J11" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="12.8">
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="1">
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -522,15 +548,18 @@
       <c r="J12" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" ht="12.8">
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="1">
         <v>3</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -539,19 +568,22 @@
       <c r="J13" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H21" s="1" t="n">
+    <row r="21" ht="22.35">
+      <c r="H21" s="1">
         <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
@@ -560,15 +592,18 @@
       <c r="J21" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" ht="12.8">
       <c r="B22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="1">
         <v>5</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -577,15 +612,18 @@
       <c r="J22" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" ht="12.8">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="1">
         <v>6</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -594,14 +632,17 @@
       <c r="J23" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" ht="12.8">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="1" t="n">
+    <row r="27" ht="12.8">
+      <c r="H27" s="1">
         <v>7</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -610,8 +651,11 @@
       <c r="J27" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
       <c r="D28" s="1" t="s">
         <v>29</v>
       </c>
@@ -619,18 +663,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.8">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H32" s="1" t="n">
+    <row r="32" ht="12.8">
+      <c r="H32" s="1">
         <v>8</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -639,20 +683,23 @@
       <c r="J32" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" ht="12.8">
       <c r="B35" s="1" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
